--- a/outputs/excel/murb_national_summary.xlsx
+++ b/outputs/excel/murb_national_summary.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Field Dictionary" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Data Quality'!$A$1:$R$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Data Quality'!$A$1:$S$16</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -42,7 +42,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -59,6 +59,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00C6EFCE"/>
         <bgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
+        <bgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
     <fill>
@@ -80,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -89,6 +95,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -455,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -477,7 +484,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-27 18:32 UTC</t>
+          <t>2026-07-27 19:03 UTC</t>
         </is>
       </c>
     </row>
@@ -549,43 +556,79 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>National inventory + sampled geometry metrics</t>
+          <t>All provinces and territories</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Sample provinces (metrics)</t>
+          <t>Total records</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>NT, YT, PE, NL</t>
+          <t>14,417,429</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Sample size per file</t>
+          <t>Geometry sample per file</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>500</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Total buildings measured</t>
+          <t>Classification sample per file</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>4000</t>
+          <t>500</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>NS MURB analysis</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2766 buildings with units &gt;= 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Archetypes</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>6 clusters from NS MURBs</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Generated</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-07-27 19:03 UTC</t>
         </is>
       </c>
     </row>
@@ -600,7 +643,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R5"/>
+  <dimension ref="A1:S16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -621,6 +664,7 @@
     <col width="15" customWidth="1" min="16" max="16"/>
     <col width="15" customWidth="1" min="17" max="17"/>
     <col width="15" customWidth="1" min="18" max="18"/>
+    <col width="15" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -641,100 +685,105 @@
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
+          <t>sources</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
           <t>id_pct</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>source_id_pct</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>source_pct</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="H1" s="3" t="inlineStr">
         <is>
           <t>dataset_pct</t>
         </is>
       </c>
-      <c r="H1" s="3" t="inlineStr">
+      <c r="I1" s="3" t="inlineStr">
         <is>
           <t>csduid_pct</t>
         </is>
       </c>
-      <c r="I1" s="3" t="inlineStr">
+      <c r="J1" s="3" t="inlineStr">
         <is>
           <t>csdname_pct</t>
         </is>
       </c>
-      <c r="J1" s="3" t="inlineStr">
+      <c r="K1" s="3" t="inlineStr">
         <is>
           <t>prov_terr_pct</t>
         </is>
       </c>
-      <c r="K1" s="3" t="inlineStr">
+      <c r="L1" s="3" t="inlineStr">
         <is>
           <t>name_pct</t>
         </is>
       </c>
-      <c r="L1" s="3" t="inlineStr">
+      <c r="M1" s="3" t="inlineStr">
         <is>
           <t>type_pct</t>
         </is>
       </c>
-      <c r="M1" s="3" t="inlineStr">
+      <c r="N1" s="3" t="inlineStr">
         <is>
           <t>address_pct</t>
         </is>
       </c>
-      <c r="N1" s="3" t="inlineStr">
+      <c r="O1" s="3" t="inlineStr">
+        <is>
+          <t>height_pct</t>
+        </is>
+      </c>
+      <c r="P1" s="3" t="inlineStr">
+        <is>
+          <t>floors_pct</t>
+        </is>
+      </c>
+      <c r="Q1" s="3" t="inlineStr">
+        <is>
+          <t>units_pct</t>
+        </is>
+      </c>
+      <c r="R1" s="3" t="inlineStr">
         <is>
           <t>year_built_pct</t>
         </is>
       </c>
-      <c r="O1" s="3" t="inlineStr">
-        <is>
-          <t>units_pct</t>
-        </is>
-      </c>
-      <c r="P1" s="3" t="inlineStr">
-        <is>
-          <t>floors_pct</t>
-        </is>
-      </c>
-      <c r="Q1" s="3" t="inlineStr">
+      <c r="S1" s="3" t="inlineStr">
         <is>
           <t>sq_ft_pct</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="inlineStr">
-        <is>
-          <t>height_pct</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>187694</v>
+        <v>1334404</v>
       </c>
       <c r="C2" t="n">
-        <v>74.90000000000001</v>
-      </c>
-      <c r="D2" s="4" t="n">
-        <v>100</v>
+        <v>572.4</v>
+      </c>
+      <c r="D2" t="n">
+        <v>12</v>
       </c>
       <c r="E2" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="F2" s="4" t="n">
-        <v>100</v>
+      <c r="F2" s="5" t="n">
+        <v>35.67</v>
       </c>
       <c r="G2" s="4" t="n">
         <v>100</v>
@@ -748,51 +797,54 @@
       <c r="J2" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="K2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" s="5" t="n">
-        <v>0</v>
+      <c r="K2" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="L2" s="6" t="n">
+        <v>0.19</v>
       </c>
       <c r="M2" s="5" t="n">
-        <v>0</v>
+        <v>38.48</v>
       </c>
       <c r="N2" s="5" t="n">
-        <v>0</v>
+        <v>40.07</v>
       </c>
       <c r="O2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R2" s="5" t="n">
+        <v>10.59</v>
+      </c>
+      <c r="P2" s="6" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="Q2" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" s="6" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>BC</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11811</v>
+        <v>1303603</v>
       </c>
       <c r="C3" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="D3" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="E3" s="5" t="n">
-        <v>2.18</v>
+        <v>618.2</v>
+      </c>
+      <c r="D3" t="n">
+        <v>30</v>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>100</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>100</v>
+        <v>85.42</v>
       </c>
       <c r="G3" s="4" t="n">
         <v>100</v>
@@ -806,45 +858,48 @@
       <c r="J3" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="K3" s="5" t="n">
+      <c r="K3" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="L3" s="6" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="M3" s="5" t="n">
+        <v>11.42</v>
+      </c>
+      <c r="N3" s="5" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="O3" s="5" t="n">
+        <v>26.51</v>
+      </c>
+      <c r="P3" s="6" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="Q3" s="6" t="n">
         <v>0.03</v>
       </c>
-      <c r="L3" s="4" t="n">
-        <v>94.91</v>
-      </c>
-      <c r="M3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" s="5" t="n">
-        <v>0</v>
+      <c r="R3" s="6" t="n">
+        <v>7.63</v>
+      </c>
+      <c r="S3" s="6" t="n">
+        <v>0.02</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>MB</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>85856</v>
+        <v>656775</v>
       </c>
       <c r="C4" t="n">
-        <v>35.4</v>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>100</v>
+        <v>298.8</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1</v>
       </c>
       <c r="E4" s="4" t="n">
         <v>100</v>
@@ -864,91 +919,768 @@
       <c r="J4" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="K4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" s="5" t="n">
+      <c r="K4" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="L4" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" s="6" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>NB</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>661827</v>
+      </c>
+      <c r="C5" t="n">
+        <v>256.6</v>
+      </c>
+      <c r="D5" t="n">
+        <v>8</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H5" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="J5" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="K5" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="L5" s="6" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="M5" s="5" t="n">
+        <v>17.81</v>
+      </c>
+      <c r="N5" s="5" t="n">
+        <v>20.79</v>
+      </c>
+      <c r="O5" s="6" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="P5" s="6" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="Q5" s="6" t="n">
+        <v>7.98</v>
+      </c>
+      <c r="R5" s="6" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="S5" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>187694</v>
+      </c>
+      <c r="C6" t="n">
+        <v>74.90000000000001</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H6" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="I6" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="J6" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="K6" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="L6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>528307</v>
+      </c>
+      <c r="C7" t="n">
+        <v>226.9</v>
+      </c>
+      <c r="D7" t="n">
+        <v>6</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>78.92</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H7" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="I7" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="J7" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="K7" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="L7" s="6" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="M7" s="5" t="n">
+        <v>25.05</v>
+      </c>
+      <c r="N7" s="5" t="n">
+        <v>25.92</v>
+      </c>
+      <c r="O7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" s="6" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="Q7" s="5" t="n">
+        <v>23.02</v>
+      </c>
+      <c r="R7" s="6" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="S7" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>11811</v>
+      </c>
+      <c r="C8" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="J8" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="K8" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="L8" s="6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="M8" s="4" t="n">
+        <v>94.91</v>
+      </c>
+      <c r="N8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="C9" t="n">
+        <v>889.5</v>
+      </c>
+      <c r="D9" t="n">
+        <v>21</v>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>96.92</v>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H9" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="I9" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="J9" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="K9" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="L9" s="6" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="M9" s="6" t="n">
+        <v>5.36</v>
+      </c>
+      <c r="N9" s="5" t="n">
+        <v>49.65</v>
+      </c>
+      <c r="O9" s="5" t="n">
+        <v>14.94</v>
+      </c>
+      <c r="P9" s="6" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="Q9" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="R9" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="S9" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="C10" t="n">
+        <v>919.7</v>
+      </c>
+      <c r="D10" t="n">
+        <v>25</v>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>84.88</v>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H10" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="I10" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="J10" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="K10" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="L10" s="6" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M10" s="5" t="n">
+        <v>12.24</v>
+      </c>
+      <c r="N10" s="4" t="n">
+        <v>57.23</v>
+      </c>
+      <c r="O10" s="5" t="n">
+        <v>16.91</v>
+      </c>
+      <c r="P10" s="6" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="Q10" s="6" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="R10" s="6" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="S10" s="6" t="n">
+        <v>3.36</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1695485</v>
+      </c>
+      <c r="C11" t="n">
+        <v>713.2</v>
+      </c>
+      <c r="D11" t="n">
+        <v>20</v>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>80.05</v>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H11" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="I11" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="J11" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="K11" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="L11" s="6" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="M11" s="5" t="n">
+        <v>25.56</v>
+      </c>
+      <c r="N11" s="5" t="n">
+        <v>29.23</v>
+      </c>
+      <c r="O11" s="6" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="P11" s="6" t="n">
+        <v>5.59</v>
+      </c>
+      <c r="Q11" s="6" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="R11" s="6" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="S11" s="6" t="n">
+        <v>4.07</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>85856</v>
+      </c>
+      <c r="C12" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H12" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="I12" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="J12" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="K12" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="L12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>QC</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="C13" t="n">
+        <v>861.9</v>
+      </c>
+      <c r="D13" t="n">
+        <v>9</v>
+      </c>
+      <c r="E13" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>81.36</v>
+      </c>
+      <c r="G13" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H13" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="I13" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="J13" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="K13" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="L13" s="6" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="M13" s="5" t="n">
+        <v>16.72</v>
+      </c>
+      <c r="N13" s="6" t="n">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="O13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>QC</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1679721</v>
+      </c>
+      <c r="C14" t="n">
+        <v>746.8</v>
+      </c>
+      <c r="D14" t="n">
+        <v>9</v>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>58.06</v>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="I14" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="J14" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="K14" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="L14" s="6" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="M14" s="6" t="n">
+        <v>5.18</v>
+      </c>
+      <c r="N14" s="5" t="n">
+        <v>18.45</v>
+      </c>
+      <c r="O14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>SK</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>259461</v>
+      </c>
+      <c r="C15" t="n">
+        <v>115.9</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="G15" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H15" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="I15" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="J15" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="K15" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="L15" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="M15" s="6" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="N15" s="5" t="n">
+        <v>25.66</v>
+      </c>
+      <c r="O15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>YT</t>
         </is>
       </c>
-      <c r="B5" t="n">
+      <c r="B16" t="n">
         <v>12485</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C16" t="n">
         <v>5.1</v>
       </c>
-      <c r="D5" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="E5" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="F5" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="G5" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="H5" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="I5" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="J5" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="K5" s="5" t="n">
+      <c r="D16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H16" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="I16" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="J16" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="K16" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="L16" s="6" t="n">
         <v>0.11</v>
       </c>
-      <c r="L5" s="5" t="n">
+      <c r="M16" s="6" t="n">
         <v>0.02</v>
       </c>
-      <c r="M5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" s="5" t="n">
+      <c r="N16" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" s="6" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R5"/>
+  <autoFilter ref="A1:S16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -982,87 +1714,87 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>field</t>
         </is>
       </c>
-      <c r="B1" s="6" t="inlineStr">
+      <c r="B1" s="7" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="C1" s="6" t="inlineStr">
+      <c r="C1" s="7" t="inlineStr">
         <is>
           <t>valid_count</t>
         </is>
       </c>
-      <c r="D1" s="6" t="inlineStr">
+      <c r="D1" s="7" t="inlineStr">
         <is>
           <t>missing_count</t>
         </is>
       </c>
-      <c r="E1" s="6" t="inlineStr">
+      <c r="E1" s="7" t="inlineStr">
         <is>
           <t>missingness_pct</t>
         </is>
       </c>
-      <c r="F1" s="6" t="inlineStr">
+      <c r="F1" s="7" t="inlineStr">
         <is>
           <t>min</t>
         </is>
       </c>
-      <c r="G1" s="6" t="inlineStr">
+      <c r="G1" s="7" t="inlineStr">
         <is>
           <t>max</t>
         </is>
       </c>
-      <c r="H1" s="6" t="inlineStr">
+      <c r="H1" s="7" t="inlineStr">
         <is>
           <t>mean</t>
         </is>
       </c>
-      <c r="I1" s="6" t="inlineStr">
+      <c r="I1" s="7" t="inlineStr">
         <is>
           <t>median</t>
         </is>
       </c>
-      <c r="J1" s="6" t="inlineStr">
+      <c r="J1" s="7" t="inlineStr">
         <is>
           <t>std</t>
         </is>
       </c>
-      <c r="K1" s="6" t="inlineStr">
+      <c r="K1" s="7" t="inlineStr">
         <is>
           <t>p5</t>
         </is>
       </c>
-      <c r="L1" s="6" t="inlineStr">
+      <c r="L1" s="7" t="inlineStr">
         <is>
           <t>p10</t>
         </is>
       </c>
-      <c r="M1" s="6" t="inlineStr">
+      <c r="M1" s="7" t="inlineStr">
         <is>
           <t>p25</t>
         </is>
       </c>
-      <c r="N1" s="6" t="inlineStr">
+      <c r="N1" s="7" t="inlineStr">
         <is>
           <t>p75</t>
         </is>
       </c>
-      <c r="O1" s="6" t="inlineStr">
+      <c r="O1" s="7" t="inlineStr">
         <is>
           <t>p90</t>
         </is>
       </c>
-      <c r="P1" s="6" t="inlineStr">
+      <c r="P1" s="7" t="inlineStr">
         <is>
           <t>p95</t>
         </is>
       </c>
-      <c r="Q1" s="6" t="inlineStr">
+      <c r="Q1" s="7" t="inlineStr">
         <is>
           <t>iqr</t>
         </is>
@@ -1075,10 +1807,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4000</v>
+        <v>7500</v>
       </c>
       <c r="C2" t="n">
-        <v>4000</v>
+        <v>7500</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -1090,37 +1822,37 @@
         <v>2.339130947358731</v>
       </c>
       <c r="G2" t="n">
-        <v>9484.956130282571</v>
+        <v>64876.52036258455</v>
       </c>
       <c r="H2" t="n">
-        <v>162.84</v>
+        <v>147.62</v>
       </c>
       <c r="I2" t="n">
-        <v>104.497097274574</v>
+        <v>90.84368221470541</v>
       </c>
       <c r="J2" t="n">
-        <v>391.16</v>
+        <v>833.51</v>
       </c>
       <c r="K2" t="n">
-        <v>10.75237375596494</v>
+        <v>11.99065021339742</v>
       </c>
       <c r="L2" t="n">
-        <v>17.10097200887231</v>
+        <v>15.17620059380091</v>
       </c>
       <c r="M2" t="n">
-        <v>48.06942074571491</v>
+        <v>33.82470163924106</v>
       </c>
       <c r="N2" t="n">
-        <v>158.5846175354405</v>
+        <v>157.3001411658541</v>
       </c>
       <c r="O2" t="n">
-        <v>256.9691156344701</v>
+        <v>234.4562544070682</v>
       </c>
       <c r="P2" t="n">
-        <v>390.898322197675</v>
+        <v>316.994434012267</v>
       </c>
       <c r="Q2" t="n">
-        <v>110.5151967897256</v>
+        <v>123.475439526613</v>
       </c>
     </row>
     <row r="3">
@@ -1130,10 +1862,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4000</v>
+        <v>7500</v>
       </c>
       <c r="C3" t="n">
-        <v>4000</v>
+        <v>7500</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -1142,40 +1874,40 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>1.000108019828054</v>
+        <v>1.000000074057476</v>
       </c>
       <c r="G3" t="n">
-        <v>12.83939917771045</v>
+        <v>47.1494687634927</v>
       </c>
       <c r="H3" t="n">
         <v>1.67</v>
       </c>
       <c r="I3" t="n">
-        <v>1.400028533612842</v>
+        <v>1.389271025365617</v>
       </c>
       <c r="J3" t="n">
-        <v>0.85</v>
+        <v>1.07</v>
       </c>
       <c r="K3" t="n">
-        <v>1.028959895102547</v>
+        <v>1.024705828792344</v>
       </c>
       <c r="L3" t="n">
-        <v>1.059317291611434</v>
+        <v>1.05357437242616</v>
       </c>
       <c r="M3" t="n">
-        <v>1.164555334337877</v>
+        <v>1.158238131504536</v>
       </c>
       <c r="N3" t="n">
-        <v>1.833643961026799</v>
+        <v>1.814972373787192</v>
       </c>
       <c r="O3" t="n">
-        <v>2.516283167850811</v>
+        <v>2.496251989195172</v>
       </c>
       <c r="P3" t="n">
-        <v>3.207472599497196</v>
+        <v>3.209924228461882</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.6690886266889216</v>
+        <v>0.6567342422826556</v>
       </c>
     </row>
     <row r="4">
@@ -1185,10 +1917,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4000</v>
+        <v>7500</v>
       </c>
       <c r="C4" t="n">
-        <v>4000</v>
+        <v>7500</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -1197,40 +1929,40 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1378109947419797</v>
+        <v>0.06169781918174338</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9978666329368803</v>
+        <v>0.9977166079376146</v>
       </c>
       <c r="H4" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6640062081056115</v>
+        <v>0.6865150812313829</v>
       </c>
       <c r="J4" t="n">
         <v>0.13</v>
       </c>
       <c r="K4" t="n">
-        <v>0.4084096068410943</v>
+        <v>0.4220116621906476</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4632157487977361</v>
+        <v>0.4864183932422264</v>
       </c>
       <c r="M4" t="n">
-        <v>0.5713305479888586</v>
+        <v>0.6006827833707</v>
       </c>
       <c r="N4" t="n">
-        <v>0.7428388861988315</v>
+        <v>0.7611017844772155</v>
       </c>
       <c r="O4" t="n">
-        <v>0.7816231697651521</v>
+        <v>0.81396233900864</v>
       </c>
       <c r="P4" t="n">
-        <v>0.8106884775384273</v>
+        <v>0.8833130286221719</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.1715083382099729</v>
+        <v>0.1604190011065155</v>
       </c>
     </row>
     <row r="5">
@@ -1240,10 +1972,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4000</v>
+        <v>7500</v>
       </c>
       <c r="C5" t="n">
-        <v>4000</v>
+        <v>7500</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -1252,40 +1984,40 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2958435632266536</v>
+        <v>0.2724016212904546</v>
       </c>
       <c r="G5" t="n">
         <v>1.000484093979574</v>
       </c>
       <c r="H5" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8768281864501156</v>
+        <v>0.8898622141639032</v>
       </c>
       <c r="J5" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6186769984018612</v>
+        <v>0.6375546399087633</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6827259780024018</v>
+        <v>0.7121689055672582</v>
       </c>
       <c r="M5" t="n">
-        <v>0.7881854582950215</v>
+        <v>0.8034168711097182</v>
       </c>
       <c r="N5" t="n">
-        <v>0.9769775023008043</v>
+        <v>0.9802984134788686</v>
       </c>
       <c r="O5" t="n">
-        <v>0.9999543378386119</v>
+        <v>0.9994514776747622</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9999997857148232</v>
+        <v>0.9999259010522948</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.1887920440057828</v>
+        <v>0.1768815423691504</v>
       </c>
     </row>
   </sheetData>
@@ -1310,27 +2042,27 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="B1" s="6" t="inlineStr">
+      <c r="B1" s="7" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="C1" s="6" t="inlineStr">
+      <c r="C1" s="7" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="D1" s="6" t="inlineStr">
+      <c r="D1" s="7" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="E1" s="6" t="inlineStr">
+      <c r="E1" s="7" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
